--- a/DataTables/Datas/__enums__.xlsx
+++ b/DataTables/Datas/__enums__.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kaboom\Downloads\Lcc-master\Lcc-master\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DD3F160-D887-455E-AA90-7BE1A75FD85F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C681728E-497E-43DD-9034-00CFB4F47E08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="64">
   <si>
     <t>##var</t>
   </si>
@@ -90,150 +90,6 @@
   </si>
   <si>
     <t>注释</t>
-  </si>
-  <si>
-    <t>BoolPropertyType</t>
-  </si>
-  <si>
-    <t>Invalid</t>
-  </si>
-  <si>
-    <t>Stunable</t>
-  </si>
-  <si>
-    <t>能不能被眩晕</t>
-  </si>
-  <si>
-    <t>Moveable</t>
-  </si>
-  <si>
-    <t>能不能移动</t>
-  </si>
-  <si>
-    <t>Skillable</t>
-  </si>
-  <si>
-    <t>能不能放技能</t>
-  </si>
-  <si>
-    <t>Hitbackable</t>
-  </si>
-  <si>
-    <t>能不能受击</t>
-  </si>
-  <si>
-    <t>Visible</t>
-  </si>
-  <si>
-    <t>能不能显示</t>
-  </si>
-  <si>
-    <t>Blockable</t>
-  </si>
-  <si>
-    <t>能不能被被碰撞</t>
-  </si>
-  <si>
-    <t>Damageable</t>
-  </si>
-  <si>
-    <t>能不能被伤害</t>
-  </si>
-  <si>
-    <t>Targetable</t>
-  </si>
-  <si>
-    <t>能不能主动碰撞</t>
-  </si>
-  <si>
-    <t>Healable</t>
-  </si>
-  <si>
-    <t>能不能回血</t>
-  </si>
-  <si>
-    <t>Dieable</t>
-  </si>
-  <si>
-    <t>能不能死亡</t>
-  </si>
-  <si>
-    <t>IsAlive</t>
-  </si>
-  <si>
-    <t>是否活着</t>
-  </si>
-  <si>
-    <t>IsStuning</t>
-  </si>
-  <si>
-    <t>是否眩晕</t>
-  </si>
-  <si>
-    <t>ValuePropertyType</t>
-  </si>
-  <si>
-    <t>Attack</t>
-  </si>
-  <si>
-    <t>Defence</t>
-  </si>
-  <si>
-    <t>MaxHp</t>
-  </si>
-  <si>
-    <t>MoveSpeed</t>
-  </si>
-  <si>
-    <t>移动速度</t>
-  </si>
-  <si>
-    <t>CriticalRate</t>
-  </si>
-  <si>
-    <t>暴击率</t>
-  </si>
-  <si>
-    <t>CriticalDamage</t>
-  </si>
-  <si>
-    <t>暴击伤害</t>
-  </si>
-  <si>
-    <t>Cure</t>
-  </si>
-  <si>
-    <t>治疗</t>
-  </si>
-  <si>
-    <t>CollisionType</t>
-  </si>
-  <si>
-    <t>Collider2D</t>
-  </si>
-  <si>
-    <t>Raycast2D</t>
-  </si>
-  <si>
-    <t>BoxCollider</t>
-  </si>
-  <si>
-    <t>Raycast</t>
-  </si>
-  <si>
-    <t>StackType</t>
-  </si>
-  <si>
-    <t>AddLevel</t>
-  </si>
-  <si>
-    <t>增加层数</t>
-  </si>
-  <si>
-    <t>AddSubBuff</t>
-  </si>
-  <si>
-    <t>增加子buff</t>
   </si>
   <si>
     <t>QualityType</t>
@@ -461,11 +317,11 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -742,7 +598,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L51"/>
+  <dimension ref="A1:L24"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="19" customWidth="1"/>
@@ -778,13 +634,13 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3"/>
-      <c r="J1" s="3"/>
-      <c r="K1" s="3"/>
-      <c r="L1" s="3"/>
+      <c r="I1" s="4"/>
+      <c r="J1" s="4"/>
+      <c r="K1" s="4"/>
+      <c r="L1" s="4"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
@@ -847,7 +703,7 @@
         <v>19</v>
       </c>
       <c r="C4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D4" t="b">
         <v>1</v>
@@ -855,468 +711,204 @@
       <c r="H4" t="s">
         <v>20</v>
       </c>
-      <c r="J4">
-        <v>0</v>
+      <c r="I4" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="H5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I5" t="s">
-        <v>22</v>
-      </c>
-      <c r="J5">
-        <v>1</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="H6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I6" t="s">
-        <v>24</v>
-      </c>
-      <c r="J6">
-        <v>2</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="H7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I7" t="s">
-        <v>26</v>
-      </c>
-      <c r="J7">
-        <v>4</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="H8" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I8" t="s">
-        <v>28</v>
-      </c>
-      <c r="J8">
-        <v>8</v>
+        <v>29</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="H9" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I9" t="s">
-        <v>30</v>
-      </c>
-      <c r="J9">
-        <v>16</v>
+        <v>31</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="H10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I10" t="s">
-        <v>32</v>
-      </c>
-      <c r="J10">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B11" t="s">
+        <v>34</v>
+      </c>
+      <c r="C11" t="b">
+        <v>0</v>
+      </c>
+      <c r="D11" t="b">
+        <v>1</v>
+      </c>
       <c r="H11" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="I11" t="s">
-        <v>34</v>
-      </c>
-      <c r="J11">
-        <v>64</v>
+        <v>36</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="H12" t="s">
+        <v>37</v>
+      </c>
+      <c r="I12" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B13" t="s">
+        <v>39</v>
+      </c>
+      <c r="C13" t="b">
+        <v>0</v>
+      </c>
+      <c r="D13" t="b">
+        <v>1</v>
+      </c>
+      <c r="H13" t="s">
         <v>35</v>
       </c>
-      <c r="I12" t="s">
+      <c r="I13" t="s">
         <v>36</v>
-      </c>
-      <c r="J12">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="H13" t="s">
-        <v>37</v>
-      </c>
-      <c r="I13" t="s">
-        <v>38</v>
-      </c>
-      <c r="J13">
-        <v>256</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="H14" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I14" t="s">
-        <v>40</v>
-      </c>
-      <c r="J14">
-        <v>512</v>
+        <v>41</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B15" t="s">
+        <v>42</v>
+      </c>
+      <c r="C15" t="b">
+        <v>0</v>
+      </c>
+      <c r="D15" t="b">
+        <v>1</v>
+      </c>
       <c r="H15" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="I15" t="s">
-        <v>42</v>
-      </c>
-      <c r="J15">
-        <v>1024</v>
+        <v>44</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="H16" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="I16" t="s">
-        <v>44</v>
-      </c>
-      <c r="J16">
-        <v>2048</v>
+        <v>46</v>
       </c>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B17" t="s">
-        <v>45</v>
-      </c>
-      <c r="C17" t="b">
-        <v>0</v>
-      </c>
-      <c r="D17" t="b">
-        <v>1</v>
-      </c>
       <c r="H17" t="s">
-        <v>20</v>
+        <v>47</v>
+      </c>
+      <c r="I17" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="18" spans="2:9" x14ac:dyDescent="0.2">
       <c r="H18" t="s">
-        <v>46</v>
+        <v>49</v>
+      </c>
+      <c r="I18" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="19" spans="2:9" x14ac:dyDescent="0.2">
       <c r="H19" t="s">
-        <v>47</v>
+        <v>51</v>
+      </c>
+      <c r="I19" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.2">
       <c r="H20" t="s">
-        <v>48</v>
+        <v>53</v>
+      </c>
+      <c r="I20" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="21" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="H21" t="s">
-        <v>49</v>
-      </c>
-      <c r="I21" t="s">
-        <v>50</v>
+      <c r="B21" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C21" t="b">
+        <v>0</v>
+      </c>
+      <c r="D21" t="b">
+        <v>1</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="I21" s="3" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="H22" t="s">
-        <v>51</v>
-      </c>
-      <c r="I22" t="s">
-        <v>52</v>
+      <c r="H22" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="23" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="H23" t="s">
-        <v>53</v>
-      </c>
-      <c r="I23" t="s">
-        <v>54</v>
+      <c r="H23" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="I23" s="3" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="H24" t="s">
-        <v>55</v>
-      </c>
-      <c r="I24" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="25" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B25" t="s">
-        <v>57</v>
-      </c>
-      <c r="C25" t="b">
-        <v>0</v>
-      </c>
-      <c r="D25" t="b">
-        <v>1</v>
-      </c>
-      <c r="H25" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="26" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="H26" t="s">
+      <c r="H24" s="3" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="27" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="H27" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="28" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="H28" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="29" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B29" t="s">
-        <v>62</v>
-      </c>
-      <c r="C29" t="b">
-        <v>0</v>
-      </c>
-      <c r="D29" t="b">
-        <v>1</v>
-      </c>
-      <c r="H29" t="s">
+      <c r="I24" s="3" t="s">
         <v>63</v>
-      </c>
-      <c r="I29" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="30" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="H30" t="s">
-        <v>65</v>
-      </c>
-      <c r="I30" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="31" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B31" t="s">
-        <v>67</v>
-      </c>
-      <c r="C31" t="b">
-        <v>0</v>
-      </c>
-      <c r="D31" t="b">
-        <v>1</v>
-      </c>
-      <c r="H31" t="s">
-        <v>68</v>
-      </c>
-      <c r="I31" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="32" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="H32" t="s">
-        <v>70</v>
-      </c>
-      <c r="I32" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="33" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="H33" t="s">
-        <v>72</v>
-      </c>
-      <c r="I33" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="34" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="H34" t="s">
-        <v>74</v>
-      </c>
-      <c r="I34" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="35" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="H35" t="s">
-        <v>76</v>
-      </c>
-      <c r="I35" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="36" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="H36" t="s">
-        <v>78</v>
-      </c>
-      <c r="I36" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="37" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="H37" t="s">
-        <v>80</v>
-      </c>
-      <c r="I37" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="38" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B38" t="s">
-        <v>82</v>
-      </c>
-      <c r="C38" t="b">
-        <v>0</v>
-      </c>
-      <c r="D38" t="b">
-        <v>1</v>
-      </c>
-      <c r="H38" t="s">
-        <v>83</v>
-      </c>
-      <c r="I38" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="39" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="H39" t="s">
-        <v>85</v>
-      </c>
-      <c r="I39" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="40" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B40" t="s">
-        <v>87</v>
-      </c>
-      <c r="C40" t="b">
-        <v>0</v>
-      </c>
-      <c r="D40" t="b">
-        <v>1</v>
-      </c>
-      <c r="H40" t="s">
-        <v>83</v>
-      </c>
-      <c r="I40" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="41" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="H41" t="s">
-        <v>88</v>
-      </c>
-      <c r="I41" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="42" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B42" t="s">
-        <v>90</v>
-      </c>
-      <c r="C42" t="b">
-        <v>0</v>
-      </c>
-      <c r="D42" t="b">
-        <v>1</v>
-      </c>
-      <c r="H42" t="s">
-        <v>91</v>
-      </c>
-      <c r="I42" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="43" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="H43" t="s">
-        <v>93</v>
-      </c>
-      <c r="I43" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="44" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="H44" t="s">
-        <v>95</v>
-      </c>
-      <c r="I44" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="45" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="H45" t="s">
-        <v>97</v>
-      </c>
-      <c r="I45" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="46" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="H46" t="s">
-        <v>99</v>
-      </c>
-      <c r="I46" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="47" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="H47" t="s">
-        <v>101</v>
-      </c>
-      <c r="I47" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="48" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B48" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="C48" t="b">
-        <v>0</v>
-      </c>
-      <c r="D48" t="b">
-        <v>1</v>
-      </c>
-      <c r="H48" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="I48" s="4" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="49" spans="8:9" x14ac:dyDescent="0.2">
-      <c r="H49" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="I49" s="4" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="50" spans="8:9" x14ac:dyDescent="0.2">
-      <c r="H50" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="I50" s="4" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="51" spans="8:9" x14ac:dyDescent="0.2">
-      <c r="H51" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="I51" s="4" t="s">
-        <v>111</v>
       </c>
     </row>
   </sheetData>
